--- a/examples/cer.xlsx
+++ b/examples/cer.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -31,16 +31,52 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F1F1F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EDEDED"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,11 +84,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -61,6 +111,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -135,6 +194,116 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. The past program's name, for the report and diagnostics.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. What the program cost, all in one dollar year and one unit (the Settings sheet says which).</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. A technical driver of cost (weight, power, lines of code). Every column of numbers here is a driver unless the Settings sheet names them.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. A technical driver of cost (weight, power, lines of code). Every column of numbers here is a driver unless the Settings sheet names them.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. yes to fit to this row, no to leave it out without deleting it.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Optional. Why a row is left out, or where the data came from.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. The new program to price.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Its value for this driver, with the same heading as on the Data sheet.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>Required. Its value for this driver, with the same heading as on the Data sheet.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>cost-core</author>
+  </authors>
+  <commentList>
+    <comment ref="A2" authorId="0" shapeId="0">
+      <text>
+        <t>The heading of the cost column on the Data sheet.</t>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0">
+      <text>
+        <t>The driver headings, separated by ;. Blank uses every other column of numbers.</t>
+      </text>
+    </comment>
+    <comment ref="A4" authorId="0" shapeId="0">
+      <text>
+        <t>log-log (cost = a * driver^b, usual for cost) or linear.</t>
+      </text>
+    </comment>
+    <comment ref="A5" authorId="0" shapeId="0">
+      <text>
+        <t>MUPE (default), OLS or ZMPE; all three are compared anyway.</t>
+      </text>
+    </comment>
+    <comment ref="A6" authorId="0" shapeId="0">
+      <text>
+        <t>The prediction interval: 0.8 for 80%.</t>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0">
+      <text>
+        <t>What the costs are in.</t>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0">
+      <text>
+        <t>The dollar year of the costs, for the record, e.g. BY2026.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -423,10 +592,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -438,313 +608,520 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Weight (lb)</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>Power (kW)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Use</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Radar A</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>27.2</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>500</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Radar B</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>51.2</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>600</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="6" t="n">
         <v>29.7</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Radar C</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" s="6" t="n">
         <v>63.9</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="6" t="n">
         <v>890</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>56.4</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="F4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Radar D</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" s="6" t="n">
         <v>68.40000000000001</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5" s="6" t="n">
         <v>1000</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>40.7</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
+      <c r="F5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Radar E</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>85.90000000000001</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6" s="6" t="n">
         <v>1060</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
+      <c r="F6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Radar F</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" s="6" t="n">
         <v>57.3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7" s="6" t="n">
         <v>1170</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>30.7</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
+      <c r="F7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Radar G</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" s="6" t="n">
         <v>97.09999999999999</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8" s="6" t="n">
         <v>1440</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="6" t="n">
         <v>41.6</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
+      <c r="F8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>Radar H</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" s="6" t="n">
         <v>96.7</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="6" t="n">
         <v>1750</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>43.5</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
+      <c r="F9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Radar I</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" s="6" t="n">
         <v>108</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10" s="6" t="n">
         <v>1770</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>36.1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
+      <c r="F10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Radar J</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" s="6" t="n">
         <v>108.6</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11" s="6" t="n">
         <v>2450</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="6" t="n">
         <v>70.7</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
+      <c r="F11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
         <is>
           <t>Radar K</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" s="6" t="n">
         <v>234.1</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12" s="6" t="n">
         <v>2890</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="6" t="n">
         <v>150</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Radar L</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" s="6" t="n">
         <v>138.1</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13" s="6" t="n">
         <v>2900</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13" s="6" t="n">
         <v>55.9</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" s="6" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+      <c r="D19" s="6" t="n"/>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n"/>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n"/>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="n"/>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="n"/>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n"/>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="n"/>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n"/>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="n"/>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n"/>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="n"/>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n"/>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="n"/>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n"/>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n"/>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="n"/>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="E2:E38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="stop">
+      <formula1>"yes,no"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -753,56 +1130,183 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Program</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Weight (lb)</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>Power (kW)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Next radar</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" s="6" t="n">
         <v>2000</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" s="6" t="n">
         <v>60</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Large radar</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" s="6" t="n">
         <v>5200</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="6" t="n">
         <v>180</v>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="n"/>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="n"/>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="n"/>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="n"/>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="n"/>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="n"/>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n"/>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="n"/>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n"/>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="n"/>
+      <c r="B19" s="6" t="n"/>
+      <c r="C19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="n"/>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n"/>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n"/>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n"/>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="n"/>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="n"/>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00FFC000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -814,111 +1318,124 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Setting</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>Cost</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>Drivers</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t>Weight (lb); Power (kW)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>Form</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>log-log</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Method</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>MUPE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Confidence</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="6" t="n">
         <v>0.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Units</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>millions</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="7" t="inlineStr">
         <is>
           <t>Dollar Year</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>BY2026</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="B4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>"log-log,linear"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>"MUPE,OLS,ZMPE"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Not one of the choices" error="Choose one of the listed answers." type="list" errorStyle="information">
+      <formula1>"dollars,thousands,millions,billions"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="00A6A6A6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -926,72 +1443,139 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>How to fill in this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Yellow cells</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Yours to fill in. The example rows are there to show the layout: type over them, and add more rows in the yellow space below.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Dark blue heading</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A column that must be filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Light blue heading</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>An optional column: leave it blank if it doesn't apply.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="11" t="inlineStr">
+        <is>
+          <t>Grey cells</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Labels: leave them as they are.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Hover over a heading</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>A note says what goes in that column, in what units, with an example. A small arrow in a cell means a drop-down list of the allowed answers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Sheet or topic</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B8" s="1" t="inlineStr">
         <is>
           <t>What to put there</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>What this is</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>The data for a cost estimating relationship (CER) and the new programs to price with it: ce-core cer --data &lt;this file&gt;. Every number in the example is invented.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>Data sheet</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>One row per past program. Program is its name; Cost is what it cost (all in one dollar year and one unit); every other column with numbers in it is a driver. Use (yes or no) leaves a row out of the fit without deleting it, and Note says why.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>Estimate sheet</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>One row per new program to price, with the same driver headings as the Data sheet. Leave it empty to fit the CER only.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>Settings sheet</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Cost and Drivers name the columns when the headings aren't the defaults (drivers separated by ;). Form is log-log (cost = a * driver^b, the usual one for cost) or linear. Method is MUPE (the default), OLS or ZMPE; all three are fitted and compared either way. Confidence is the prediction interval (0.8 for 80%). Units and Dollar Year are for the record.</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>Reading the result</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>The prediction interval is where one new program is expected to land, which is what an estimate needs; it is wider than the confidence interval on the line itself, and it never shrinks below the scatter of the data. A new program outside the range of the data is flagged: the CER has no evidence there.</t>
         </is>
